--- a/source_data/Fig4.xlsx
+++ b/source_data/Fig4.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Panel a: portfolio that up to 1% of GDP a year buys in each of the 30 economies; cost premium, security margin and net premium in US$ per tonne of CO2 displaced, carbon price in force; justified when the net premium does not exceed the carbon price</t>
+          <t>Panel a: portfolio that up to 1% of GDP a year buys in each of the 30 economies; cost premium, security margin and net premium in US$ per tonne of CO2 displaced, carbon price in force; justified when the net premium does not exceed the carbon price (green ring); the security margin is the arrow from the open to the filled circle. first_justified_cost_year groups the rows (empty: not justified at any cost year); net_importer = False marks the economies below the dashed line</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CO2 displaced with the security value and on cost alone (dashed and dotted lines)</t>
+          <t>CO2 displaced with the security value and on cost alone (dashed and dotted lines), and the CO2 of blocks above the top of the axis (US$300 per tCO2), in GtCO2 per year</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,11 @@
           <t>justified</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>first_justified_cost_year</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -594,6 +599,9 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
+      <c r="K2" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -628,6 +636,7 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -662,6 +671,7 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -696,6 +706,7 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -730,6 +741,9 @@
       <c r="J6" t="b">
         <v>1</v>
       </c>
+      <c r="K6" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -764,6 +778,7 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -798,6 +813,7 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -832,6 +848,7 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -866,6 +883,9 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
+      <c r="K10" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -900,6 +920,9 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
+      <c r="K11" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -934,6 +957,9 @@
       <c r="J12" t="b">
         <v>1</v>
       </c>
+      <c r="K12" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -968,6 +994,9 @@
       <c r="J13" t="b">
         <v>1</v>
       </c>
+      <c r="K13" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1002,6 +1031,9 @@
       <c r="J14" t="b">
         <v>1</v>
       </c>
+      <c r="K14" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1036,6 +1068,9 @@
       <c r="J15" t="b">
         <v>1</v>
       </c>
+      <c r="K15" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1070,6 +1105,7 @@
       <c r="J16" t="b">
         <v>0</v>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1104,6 +1140,7 @@
       <c r="J17" t="b">
         <v>0</v>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1138,6 +1175,7 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1172,6 +1210,9 @@
       <c r="J19" t="b">
         <v>0</v>
       </c>
+      <c r="K19" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1206,6 +1247,9 @@
       <c r="J20" t="b">
         <v>0</v>
       </c>
+      <c r="K20" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1240,6 +1284,7 @@
       <c r="J21" t="b">
         <v>0</v>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1274,6 +1319,9 @@
       <c r="J22" t="b">
         <v>1</v>
       </c>
+      <c r="K22" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1308,6 +1356,9 @@
       <c r="J23" t="b">
         <v>0</v>
       </c>
+      <c r="K23" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1342,6 +1393,9 @@
       <c r="J24" t="b">
         <v>1</v>
       </c>
+      <c r="K24" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1376,6 +1430,9 @@
       <c r="J25" t="b">
         <v>1</v>
       </c>
+      <c r="K25" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1410,6 +1467,9 @@
       <c r="J26" t="b">
         <v>0</v>
       </c>
+      <c r="K26" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1444,6 +1504,7 @@
       <c r="J27" t="b">
         <v>0</v>
       </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1476,6 +1537,7 @@
       <c r="J28" t="b">
         <v>0</v>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1510,6 +1572,7 @@
       <c r="J29" t="b">
         <v>0</v>
       </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1544,6 +1607,7 @@
       <c r="J30" t="b">
         <v>0</v>
       </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1578,6 +1642,7 @@
       <c r="J31" t="b">
         <v>0</v>
       </c>
+      <c r="K31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21229,7 +21294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21283,6 +21348,11 @@
           <t>justified</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>first_justified_cost_year</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21317,6 +21387,9 @@
       <c r="J2" t="b">
         <v>1</v>
       </c>
+      <c r="K2" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21351,6 +21424,7 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21385,6 +21459,7 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21419,6 +21494,7 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21453,6 +21529,9 @@
       <c r="J6" t="b">
         <v>1</v>
       </c>
+      <c r="K6" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21487,6 +21566,7 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21521,6 +21601,7 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21555,6 +21636,7 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21589,6 +21671,9 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
+      <c r="K10" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21623,6 +21708,9 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
+      <c r="K11" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21657,6 +21745,9 @@
       <c r="J12" t="b">
         <v>1</v>
       </c>
+      <c r="K12" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21691,6 +21782,9 @@
       <c r="J13" t="b">
         <v>1</v>
       </c>
+      <c r="K13" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21725,6 +21819,9 @@
       <c r="J14" t="b">
         <v>1</v>
       </c>
+      <c r="K14" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21759,6 +21856,9 @@
       <c r="J15" t="b">
         <v>1</v>
       </c>
+      <c r="K15" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21793,6 +21893,7 @@
       <c r="J16" t="b">
         <v>0</v>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21827,6 +21928,7 @@
       <c r="J17" t="b">
         <v>0</v>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21861,6 +21963,7 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21895,6 +21998,9 @@
       <c r="J19" t="b">
         <v>1</v>
       </c>
+      <c r="K19" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21929,6 +22035,9 @@
       <c r="J20" t="b">
         <v>0</v>
       </c>
+      <c r="K20" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -21963,6 +22072,7 @@
       <c r="J21" t="b">
         <v>0</v>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -21997,6 +22107,9 @@
       <c r="J22" t="b">
         <v>1</v>
       </c>
+      <c r="K22" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -22031,6 +22144,9 @@
       <c r="J23" t="b">
         <v>1</v>
       </c>
+      <c r="K23" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22065,6 +22181,9 @@
       <c r="J24" t="b">
         <v>1</v>
       </c>
+      <c r="K24" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -22099,6 +22218,9 @@
       <c r="J25" t="b">
         <v>1</v>
       </c>
+      <c r="K25" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -22133,6 +22255,9 @@
       <c r="J26" t="b">
         <v>0</v>
       </c>
+      <c r="K26" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -22167,6 +22292,7 @@
       <c r="J27" t="b">
         <v>0</v>
       </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -22199,6 +22325,7 @@
       <c r="J28" t="b">
         <v>0</v>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -22233,6 +22360,7 @@
       <c r="J29" t="b">
         <v>0</v>
       </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -22267,6 +22395,7 @@
       <c r="J30" t="b">
         <v>0</v>
       </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -22301,6 +22430,7 @@
       <c r="J31" t="b">
         <v>0</v>
       </c>
+      <c r="K31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -53379,7 +53509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53433,6 +53563,11 @@
           <t>justified</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>first_justified_cost_year</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -53467,6 +53602,9 @@
       <c r="J2" t="b">
         <v>1</v>
       </c>
+      <c r="K2" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -53501,6 +53639,7 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -53535,6 +53674,7 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -53569,6 +53709,7 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -53603,6 +53744,9 @@
       <c r="J6" t="b">
         <v>1</v>
       </c>
+      <c r="K6" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -53637,6 +53781,7 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -53671,6 +53816,7 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -53705,6 +53851,7 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -53739,6 +53886,9 @@
       <c r="J10" t="b">
         <v>1</v>
       </c>
+      <c r="K10" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -53773,6 +53923,9 @@
       <c r="J11" t="b">
         <v>1</v>
       </c>
+      <c r="K11" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -53807,6 +53960,9 @@
       <c r="J12" t="b">
         <v>1</v>
       </c>
+      <c r="K12" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -53841,6 +53997,9 @@
       <c r="J13" t="b">
         <v>1</v>
       </c>
+      <c r="K13" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -53875,6 +54034,9 @@
       <c r="J14" t="b">
         <v>1</v>
       </c>
+      <c r="K14" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -53909,6 +54071,9 @@
       <c r="J15" t="b">
         <v>1</v>
       </c>
+      <c r="K15" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -53943,6 +54108,7 @@
       <c r="J16" t="b">
         <v>0</v>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -53977,6 +54143,7 @@
       <c r="J17" t="b">
         <v>0</v>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -54011,6 +54178,7 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -54045,6 +54213,9 @@
       <c r="J19" t="b">
         <v>1</v>
       </c>
+      <c r="K19" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54079,6 +54250,9 @@
       <c r="J20" t="b">
         <v>1</v>
       </c>
+      <c r="K20" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54113,6 +54287,7 @@
       <c r="J21" t="b">
         <v>0</v>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54147,6 +54322,9 @@
       <c r="J22" t="b">
         <v>1</v>
       </c>
+      <c r="K22" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -54181,6 +54359,9 @@
       <c r="J23" t="b">
         <v>1</v>
       </c>
+      <c r="K23" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -54215,6 +54396,9 @@
       <c r="J24" t="b">
         <v>1</v>
       </c>
+      <c r="K24" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -54249,6 +54433,9 @@
       <c r="J25" t="b">
         <v>1</v>
       </c>
+      <c r="K25" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -54283,6 +54470,9 @@
       <c r="J26" t="b">
         <v>1</v>
       </c>
+      <c r="K26" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -54317,6 +54507,7 @@
       <c r="J27" t="b">
         <v>0</v>
       </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -54349,6 +54540,7 @@
       <c r="J28" t="b">
         <v>0</v>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -54383,6 +54575,7 @@
       <c r="J29" t="b">
         <v>0</v>
       </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -54417,6 +54610,7 @@
       <c r="J30" t="b">
         <v>0</v>
       </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -54451,6 +54645,7 @@
       <c r="J31" t="b">
         <v>0</v>
       </c>
+      <c r="K31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -94226,7 +94421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94245,6 +94440,11 @@
           <t>co2_displaced_cost_only_gtco2</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>co2_above_axis_top_gtco2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -94256,6 +94456,9 @@
       <c r="C2" t="n">
         <v>0.274</v>
       </c>
+      <c r="D2" t="n">
+        <v>3.33</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -94267,6 +94470,9 @@
       <c r="C3" t="n">
         <v>0.785</v>
       </c>
+      <c r="D3" t="n">
+        <v>1.407</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -94277,6 +94483,9 @@
       </c>
       <c r="C4" t="n">
         <v>1.19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.553</v>
       </c>
     </row>
   </sheetData>
